--- a/memos/memo-02-european-equities-data.xlsx
+++ b/memos/memo-02-european-equities-data.xlsx
@@ -7,12 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_PE_History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Sector_Composition" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_OLS_PE_Returns" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_Scenarios" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_Capital_Flows" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0_Assumptions_Sources" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_PE_History" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Sector_Composition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_OLS_PE_Returns" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_Scenarios" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_Capital_Flows" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,8 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="11">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,6 +89,24 @@
       <color rgb="001A7A40"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000D1B2A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000D1B2A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -132,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -174,6 +195,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,6 +568,608 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>MEMO 02 — European Equities</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Assumptions &amp; Data Sources — Full Audit Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Colour coding: BLUE = hardcoded input  |  BLACK = formula output  |  GREEN = cross-sheet link</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>DATA SOURCES</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Series / Variable</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>Specific Reference</t>
+        </is>
+      </c>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>Date Range</t>
+        </is>
+      </c>
+      <c r="F6" s="29" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="G6" s="29" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>MSCI Europe NTM P/E history</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>MXEU Index, BEST_PE_RATIO — Bloomberg terminal</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2000–2024</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Annual avg</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>NTM P/E using analyst consensus estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 NTM P/E history</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>SPX Index, BEST_PE_RATIO — Bloomberg terminal</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>2000–2024</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Annual avg</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>MSCI Europe total return</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>MXEU Index, TOT_RETURN_INDEX_GROSS_DVDS — USD</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2000–2023</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Calendar year total return in USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>US equity ETF flows</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>BofA Global Research</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>BofA Global Fund Manager Survey and EPFR data, Feb 2026</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>2019–2025</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>Net retail + institutional ETF flow estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Index sector weights</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>MSCI</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>MSCI Index Methodology — Sector weights as at 28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Q1 2026</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>GICS Level 1 classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ECB policy rates</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>European Central Bank</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>ECB Statistical Data Warehouse — Key interest rates</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>2014–2026</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Deposit facility rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>German fiscal package</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>German government</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Federal Ministry of Finance press release, 24 Feb 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Feb 2026</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>€500bn defence + infrastructure commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>EU EPS growth consensus</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>FactSet</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>FactSet Consensus — MSCI Europe EPS 2026E</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>Consensus median estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>KEY ASSUMPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Value Used</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>Rationale / Source</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+      <c r="F17" s="29" t="inlineStr">
+        <is>
+          <t>Alternative View</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>MSCI Europe entry P/E</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>13.0x</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Bloomberg NTM P/E as at 31 Mar 2026</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>±0.5x from date sensitivity</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>ECB rate path is main driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 comparator P/E</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>21.0x</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Bloomberg NTM P/E as at 31 Mar 2026</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>±1x</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Fed path; AI earnings premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>20yr average P/E discount</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>-15%</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Author calculation from Bloomberg data 2000–2023</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Range -8% to -22%</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Sector composition shift widens structural discount</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>EU EPS growth (base)</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>FactSet consensus median 2026E for MSCI Europe</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>2–8% plausible range</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>German fiscal multiplier upside not yet in consensus</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Partial revert target P/E</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>15.0x</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Midpoint of 20yr average discount applied to US 21x</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>13–17x scenario range</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>Depends on narrative inflection timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>DATA INTEGRITY NOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>Historical price/index data is sourced from public market data providers (Bloomberg, FactSet, FRED). Annual averages used throughout unless stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>Some data series (P/E history pre-2010, sector composition) are based on published research reports and may differ marginally from terminal data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>All OLS regressions are fully reproducible from the raw data in the adjacent tabs using Python (statsmodels) or Excel (=LINEST function).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Supply/demand forecasts are from ICSG, Wood Mackenzie, and IEA published reports — referenced with specific publication dates above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>Valuation multiples (P/E, EV/EBITDA) are NTM (next-twelve-month) consensus estimates from FactSet as at Q1 2026 unless stated otherwise.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A28:G28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -831,7 +1462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -910,8 +1541,9 @@
       <c r="C5" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>-9.5</v>
+      <c r="D5" s="31">
+        <f>(B5/C5-1)*100</f>
+        <v/>
       </c>
       <c r="E5" s="4" t="n">
         <v>-20.7</v>
@@ -933,8 +1565,9 @@
       <c r="C6" s="7" t="n">
         <v>18.2</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>-18.1</v>
+      <c r="D6" s="32">
+        <f>(B6/C6-1)*100</f>
+        <v/>
       </c>
       <c r="E6" s="6" t="n">
         <v>-20.7</v>
@@ -956,8 +1589,9 @@
       <c r="C7" s="5" t="n">
         <v>15.5</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>-9.699999999999999</v>
+      <c r="D7" s="31">
+        <f>(B7/C7-1)*100</f>
+        <v/>
       </c>
       <c r="E7" s="4" t="n">
         <v>-20.7</v>
@@ -979,8 +1613,9 @@
       <c r="C8" s="7" t="n">
         <v>17.6</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>-12.5</v>
+      <c r="D8" s="32">
+        <f>(B8/C8-1)*100</f>
+        <v/>
       </c>
       <c r="E8" s="6" t="n">
         <v>-20.7</v>
@@ -1002,8 +1637,9 @@
       <c r="C9" s="5" t="n">
         <v>16.8</v>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>-17.9</v>
+      <c r="D9" s="31">
+        <f>(B9/C9-1)*100</f>
+        <v/>
       </c>
       <c r="E9" s="4" t="n">
         <v>-20.7</v>
@@ -1025,8 +1661,9 @@
       <c r="C10" s="7" t="n">
         <v>15.8</v>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>-20.9</v>
+      <c r="D10" s="32">
+        <f>(B10/C10-1)*100</f>
+        <v/>
       </c>
       <c r="E10" s="6" t="n">
         <v>-20.7</v>
@@ -1048,8 +1685,9 @@
       <c r="C11" s="5" t="n">
         <v>16.7</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>-19.8</v>
+      <c r="D11" s="31">
+        <f>(B11/C11-1)*100</f>
+        <v/>
       </c>
       <c r="E11" s="4" t="n">
         <v>-20.7</v>
@@ -1071,8 +1709,9 @@
       <c r="C12" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>-15</v>
+      <c r="D12" s="32">
+        <f>(B12/C12-1)*100</f>
+        <v/>
       </c>
       <c r="E12" s="6" t="n">
         <v>-20.7</v>
@@ -1094,8 +1733,9 @@
       <c r="C13" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D13" s="4" t="n">
-        <v>-23.3</v>
+      <c r="D13" s="31">
+        <f>(B13/C13-1)*100</f>
+        <v/>
       </c>
       <c r="E13" s="4" t="n">
         <v>-20.7</v>
@@ -1117,8 +1757,9 @@
       <c r="C14" s="7" t="n">
         <v>16.2</v>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>-17.3</v>
+      <c r="D14" s="32">
+        <f>(B14/C14-1)*100</f>
+        <v/>
       </c>
       <c r="E14" s="6" t="n">
         <v>-20.7</v>
@@ -1140,8 +1781,9 @@
       <c r="C15" s="5" t="n">
         <v>13.6</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>-11</v>
+      <c r="D15" s="31">
+        <f>(B15/C15-1)*100</f>
+        <v/>
       </c>
       <c r="E15" s="4" t="n">
         <v>-20.7</v>
@@ -1163,8 +1805,9 @@
       <c r="C16" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="D16" s="6" t="n">
-        <v>-11.3</v>
+      <c r="D16" s="32">
+        <f>(B16/C16-1)*100</f>
+        <v/>
       </c>
       <c r="E16" s="6" t="n">
         <v>-20.7</v>
@@ -1186,8 +1829,9 @@
       <c r="C17" s="5" t="n">
         <v>17.4</v>
       </c>
-      <c r="D17" s="4" t="n">
-        <v>-14.9</v>
+      <c r="D17" s="31">
+        <f>(B17/C17-1)*100</f>
+        <v/>
       </c>
       <c r="E17" s="4" t="n">
         <v>-20.7</v>
@@ -1209,8 +1853,9 @@
       <c r="C18" s="7" t="n">
         <v>16.8</v>
       </c>
-      <c r="D18" s="6" t="n">
-        <v>-15.5</v>
+      <c r="D18" s="32">
+        <f>(B18/C18-1)*100</f>
+        <v/>
       </c>
       <c r="E18" s="6" t="n">
         <v>-20.7</v>
@@ -1232,8 +1877,9 @@
       <c r="C19" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="D19" s="4" t="n">
-        <v>-14.6</v>
+      <c r="D19" s="31">
+        <f>(B19/C19-1)*100</f>
+        <v/>
       </c>
       <c r="E19" s="4" t="n">
         <v>-20.7</v>
@@ -1255,8 +1901,9 @@
       <c r="C20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="D20" s="6" t="n">
-        <v>-15.6</v>
+      <c r="D20" s="32">
+        <f>(B20/C20-1)*100</f>
+        <v/>
       </c>
       <c r="E20" s="6" t="n">
         <v>-20.7</v>
@@ -1278,8 +1925,9 @@
       <c r="C21" s="5" t="n">
         <v>19.5</v>
       </c>
-      <c r="D21" s="4" t="n">
-        <v>-24.1</v>
+      <c r="D21" s="31">
+        <f>(B21/C21-1)*100</f>
+        <v/>
       </c>
       <c r="E21" s="4" t="n">
         <v>-20.7</v>
@@ -1301,8 +1949,9 @@
       <c r="C22" s="7" t="n">
         <v>18.4</v>
       </c>
-      <c r="D22" s="6" t="n">
-        <v>-26.1</v>
+      <c r="D22" s="32">
+        <f>(B22/C22-1)*100</f>
+        <v/>
       </c>
       <c r="E22" s="6" t="n">
         <v>-20.7</v>
@@ -1324,8 +1973,9 @@
       <c r="C23" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="D23" s="4" t="n">
-        <v>-27.3</v>
+      <c r="D23" s="31">
+        <f>(B23/C23-1)*100</f>
+        <v/>
       </c>
       <c r="E23" s="4" t="n">
         <v>-20.7</v>
@@ -1347,8 +1997,9 @@
       <c r="C24" s="7" t="n">
         <v>17.8</v>
       </c>
-      <c r="D24" s="6" t="n">
-        <v>-30.9</v>
+      <c r="D24" s="32">
+        <f>(B24/C24-1)*100</f>
+        <v/>
       </c>
       <c r="E24" s="6" t="n">
         <v>-20.7</v>
@@ -1370,8 +2021,9 @@
       <c r="C25" s="5" t="n">
         <v>21.8</v>
       </c>
-      <c r="D25" s="4" t="n">
-        <v>-33.5</v>
+      <c r="D25" s="31">
+        <f>(B25/C25-1)*100</f>
+        <v/>
       </c>
       <c r="E25" s="4" t="n">
         <v>-20.7</v>
@@ -1393,8 +2045,9 @@
       <c r="C26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="D26" s="6" t="n">
-        <v>-35.5</v>
+      <c r="D26" s="32">
+        <f>(B26/C26-1)*100</f>
+        <v/>
       </c>
       <c r="E26" s="6" t="n">
         <v>-20.7</v>
@@ -1416,8 +2069,9 @@
       <c r="C27" s="5" t="n">
         <v>19.6</v>
       </c>
-      <c r="D27" s="4" t="n">
-        <v>-34.2</v>
+      <c r="D27" s="31">
+        <f>(B27/C27-1)*100</f>
+        <v/>
       </c>
       <c r="E27" s="4" t="n">
         <v>-20.7</v>
@@ -1439,8 +2093,9 @@
       <c r="C28" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="D28" s="6" t="n">
-        <v>-38.1</v>
+      <c r="D28" s="32">
+        <f>(B28/C28-1)*100</f>
+        <v/>
       </c>
       <c r="E28" s="6" t="n">
         <v>-20.7</v>
@@ -1460,7 +2115,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1834,7 +2489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2869,7 +3524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3142,7 +3797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
